--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544328.0203541789</v>
+        <v>544328</v>
       </c>
       <c r="R2" t="n">
-        <v>6261506.168889094</v>
+        <v>6261506</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544228.9689827869</v>
+        <v>544229</v>
       </c>
       <c r="R3" t="n">
-        <v>6261404.671529721</v>
+        <v>6261405</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1068-2021 artfynd.xlsx
+++ b/artfynd/A 1068-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74601011</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74857523</v>
       </c>
       <c r="B3" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
